--- a/survey_templates/040_employee_collaboration_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/040_employee_collaboration_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>communication_questions_page</t>
+          <t>communication_questions_page_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Communication Questions Page 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>collaboration_questions_page</t>
+          <t>collaboration_questions_page_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>collaboration_questions_page_2</t>
+          <t>collaboration_questions_page_2_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feedback_page</t>
+          <t>feedback_page_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Feedback Page 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>collaboration_satisfaction_question_page</t>
+          <t>collaboration_satisfaction_question_page_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>collaboration_satisfaction_question_page_2</t>
+          <t>collaboration_satisfaction_question_page_2_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>Collaboration Satisfaction Question Page 2 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>communication_questions_page_2</t>
+          <t>communication_questions_page_2_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>Teamwork Page Questions</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Communication Page Questions</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>communication_questions_page_2</t>
+          <t>communication_questions_page_2_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>manager_questions_page_2</t>
+          <t>manager_questions_page_2_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>questions-2</t>
+          <t>Manager Questions Page 2 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Questions Page</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1267,63 +1267,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>communication_questions_page_choices</t>
+          <t>communication_questions_page_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>communication_questions_page_choices</t>
+          <t>communication_questions_page_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>communication_questions_page_choices</t>
+          <t>communication_questions_page_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1369,114 +1369,114 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>collaboration_questions_page_choices</t>
+          <t>collaboration_questions_page_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>collaboration_questions_page_choices</t>
+          <t>collaboration_questions_page_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>collaboration_questions_page_choices</t>
+          <t>collaboration_questions_page_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>collaboration_satisfaction_question_page_choices</t>
+          <t>collaboration_satisfaction_question_page_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>collaboration_satisfaction_question_page_choices</t>
+          <t>collaboration_satisfaction_question_page_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>collaboration_satisfaction_question_page_choices</t>
+          <t>collaboration_satisfaction_question_page_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1522,63 +1522,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>communication_questions_page_2_choices</t>
+          <t>communication_questions_page_2_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>communication_questions_page_2_choices</t>
+          <t>communication_questions_page_2_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>communication_questions_page_2_choices</t>
+          <t>communication_questions_page_2_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'very-satisfied',_'value':_'very_satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'very-satisfied', 'value': 'Very Satisfied'}</t>
+          <t>very-satisfied</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat-satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'somewhat-satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>somewhat-satisfied</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'not-at-all-satisfied',_'value':_'not_at_all_satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'not-at-all-satisfied', 'value': 'Not at all Satisfied'}</t>
+          <t>not-at-all-satisfied</t>
         </is>
       </c>
     </row>
